--- a/test_cases/wscc9_connected.xlsx
+++ b/test_cases/wscc9_connected.xlsx
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H2" s="4">
         <v>0.11</v>
@@ -2424,7 +2424,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -2652,7 +2652,6 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
